--- a/data/trans_dic/IP11D_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han sufrido algún tipo de agresión</t>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 17,85</t>
+          <t>1,66; 17,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 9,74</t>
+          <t>0,47; 9,9</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,93</t>
+          <t>0,33; 2,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,53</t>
+          <t>0,25; 1,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,34</t>
+          <t>0,41; 1,45</t>
         </is>
       </c>
     </row>
@@ -676,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,85</t>
+          <t>0,46; 3,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,53</t>
+          <t>0,44; 2,52</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,65</t>
+          <t>0,33; 1,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,35</t>
+          <t>0,64; 2,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,7</t>
+          <t>0,64; 1,7</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1028; 11093</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>548; 11551</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4186</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3455</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7640</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1502; 9771</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1278; 7812</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4008; 14182</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4208</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>843; 6834</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1459; 8387</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5394</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9687</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15080</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2184; 10072</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4904; 18281</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9135; 24286</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11D_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Estudios-trans_dic.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 17,89</t>
+          <t>0,86; 15,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 9,9</t>
+          <t>0,48; 10,76</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,13</t>
+          <t>0,34; 1,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,51</t>
+          <t>0,24; 1,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,45</t>
+          <t>0,4; 1,38</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,73</t>
+          <t>0,35; 3,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,52</t>
+          <t>0,44; 2,82</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,52</t>
+          <t>0,39; 1,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,4</t>
+          <t>0,63; 2,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,7</t>
+          <t>0,63; 1,72</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1028; 11093</t>
+          <t>535; 9851</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>548; 11551</t>
+          <t>562; 12557</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1502; 9771</t>
+          <t>1572; 8784</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1278; 7812</t>
+          <t>1216; 8735</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4008; 14182</t>
+          <t>3881; 13424</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4208</t>
+          <t>0; 4416</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>843; 6834</t>
+          <t>647; 6722</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1459; 8387</t>
+          <t>1463; 9391</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2184; 10072</t>
+          <t>2601; 10632</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4904; 18281</t>
+          <t>4791; 17811</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9135; 24286</t>
+          <t>8978; 24506</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11D_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,77; 17,26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,86; 15,89</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 10,76</t>
+          <t>0,41; 8,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,91</t>
+          <t>0,24; 1,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,69</t>
+          <t>0,39; 2,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,38</t>
+          <t>0,4; 1,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,38; 3,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,67</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,82</t>
+          <t>0,39; 2,43</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,6</t>
+          <t>0,63; 2,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,34</t>
+          <t>0,37; 1,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,72</t>
+          <t>0,63; 1,71</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3616</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3088</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>434; 9792</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>535; 9851</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>562; 12557</t>
+          <t>420; 9240</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7311</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1572; 8784</t>
+          <t>1134; 7263</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1216; 8735</t>
+          <t>1688; 8893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3881; 13424</t>
+          <t>3656; 13079</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3690</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4416</t>
+          <t>646; 6352</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>647; 6722</t>
+          <t>0; 4448</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1463; 9391</t>
+          <t>1245; 7732</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14089</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2601; 10632</t>
+          <t>4394; 16081</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4791; 17811</t>
+          <t>2320; 10748</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8978; 24506</t>
+          <t>8359; 22675</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11D_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,77; 17,26</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,41; 8,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,24; 1,53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 2,06</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,4; 1,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 3,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 2,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,63; 2,3</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 1,71</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,63; 1,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.05443222110252937</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.02983927068030535</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3088</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3088</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.007658330058197083</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>0.004061292910143622</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>434; 9792</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>420; 9240</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1725957230896583</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>0.08928727845655458</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +603,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.006583975717496734</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.009704626317558822</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.00806943969785791</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3126</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4185</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7311</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.002387933773185068</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.003913912722312065</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.004035943434195434</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1134; 7263</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1688; 8893</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3656; 13079</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.01530006069815125</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.02062071324392182</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.0144365729066312</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +658,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.014376381954345</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.008460415064249931</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01158973258261745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.003837465305570022</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.003909652612225995</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>646; 6352</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4448</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1245; 7732</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.03771558094263448</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.02965727432431285</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.02428401579161591</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.0123378004086516</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.008684909465173902</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01061022971607259</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>8635</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5454</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14089</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.006277824861681523</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.003694492179127676</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.006294970136461527</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>4394; 16081</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2320; 10748</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>8359; 22675</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.02297678214419805</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.01711485556670218</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.01707652167977699</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +777,372 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>3088</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>434</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>9792</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="n">
+        <v>9240</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3126</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>4185</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7311</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1134</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1688</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>7263</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>8893</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>13079</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2421</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1269</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>646</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>6352</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>4448</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>8635</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>5454</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>14089</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>4394</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>2320</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>8359</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>16081</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>10748</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>22675</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>